--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/DISTRICT_OF_COLUMBIA_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/DISTRICT_OF_COLUMBIA_2013.xlsx
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>General Felipe _Ngeles</t>
+          <t>General Felipe Angeles</t>
         </is>
       </c>
       <c r="C103">
